--- a/tools/menu-workbook/menu-data.xlsx
+++ b/tools/menu-workbook/menu-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\BackUp\AI+网络项目孵化\Baby_Menu_Applet\tools\menu-workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7AADDE0-8D48-44EA-BBCF-71F48B4700C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF86D68-6167-4B7B-BD07-A9CF02A6AF3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7005" yWindow="4065" windowWidth="28995" windowHeight="15555" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,8 @@
     <sheet name="Dishes" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Categories!$A$1:$C$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Dishes!$A$1:$J$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Categories!$A$1:$C$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Dishes!$A$1:$J$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Shop!$A$1:$G$2</definedName>
   </definedNames>
   <calcPr calcId="181029" forceFullCalc="1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="294">
   <si>
     <t>菜单数据维护说明</t>
   </si>
@@ -147,108 +147,72 @@
     <t>茉莉奶白</t>
   </si>
   <si>
-    <t>101</t>
-  </si>
-  <si>
     <t>GOOD ME</t>
   </si>
   <si>
     <t>古茗</t>
   </si>
   <si>
-    <t>102</t>
-  </si>
-  <si>
     <t>NO YEYE NO TEA</t>
   </si>
   <si>
     <t>爷爷不泡茶</t>
   </si>
   <si>
-    <t>103</t>
-  </si>
-  <si>
     <t>HEYTEA</t>
   </si>
   <si>
     <t>喜茶</t>
   </si>
   <si>
-    <t>104</t>
-  </si>
-  <si>
     <t>ChaPanda</t>
   </si>
   <si>
     <t>茶百道</t>
   </si>
   <si>
-    <t>105</t>
-  </si>
-  <si>
     <t>azcf</t>
   </si>
   <si>
     <t>阿正茶夫</t>
   </si>
   <si>
-    <t>106</t>
-  </si>
-  <si>
     <t>A LITTLE TEA</t>
   </si>
   <si>
     <t>一点点</t>
   </si>
   <si>
-    <t>107</t>
-  </si>
-  <si>
     <t>NAYUKI</t>
   </si>
   <si>
     <t>奈雪的茶</t>
   </si>
   <si>
-    <t>108</t>
-  </si>
-  <si>
     <t>COTTI COFFEE</t>
   </si>
   <si>
     <t>库迪</t>
   </si>
   <si>
-    <t>109</t>
-  </si>
-  <si>
     <t>luckin coffee</t>
   </si>
   <si>
     <t>瑞幸</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>AUNTEA JENNY</t>
   </si>
   <si>
     <t>沪上阿姨</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>dishId</t>
   </si>
   <si>
     <t>dishName</t>
   </si>
   <si>
-    <t>desc</t>
-  </si>
-  <si>
     <t>price</t>
   </si>
   <si>
@@ -261,55 +225,13 @@
     <t>options</t>
   </si>
   <si>
-    <t>rice01</t>
-  </si>
-  <si>
-    <t>黑椒牛肉饭</t>
-  </si>
-  <si>
-    <t>黑椒酱汁裹住鲜嫩牛肉，搭配时蔬和米饭，适合做一份饱足主食。</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
-    <t>beef-rice.jpg</t>
-  </si>
-  <si>
-    <t>招牌、推荐</t>
-  </si>
-  <si>
-    <t>口味: 原味、少辣、黑椒加浓</t>
-  </si>
-  <si>
-    <t>noodle01</t>
-  </si>
-  <si>
-    <t>番茄鸡蛋面</t>
-  </si>
-  <si>
-    <t>酸甜番茄汤底，配软嫩鸡蛋和劲道面条，清爽但不寡淡。</t>
-  </si>
-  <si>
-    <t>tomato-noodle.jpg</t>
-  </si>
-  <si>
-    <t>清爽</t>
-  </si>
-  <si>
-    <t>面条口感: 偏软、正常、劲道</t>
-  </si>
-  <si>
     <t>dessert01</t>
   </si>
   <si>
     <t>榴莲千层</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>chicken-soup.jpg</t>
   </si>
   <si>
     <t>Come Wonka01</t>
@@ -512,9 +434,6 @@
     <t>荔枝</t>
   </si>
   <si>
-    <t>夏季时令水果，果肉清甜多汁。按常见饮食说法偏温热，吃多了容易上火。</t>
-  </si>
-  <si>
     <t>lychee.jpg</t>
   </si>
   <si>
@@ -527,9 +446,6 @@
     <t>西瓜</t>
   </si>
   <si>
-    <t>夏季代表水果，清甜多汁。按常见饮食说法偏寒凉，适合做清爽解腻的展示项。</t>
-  </si>
-  <si>
     <t>watermelon.jpg</t>
   </si>
   <si>
@@ -542,9 +458,6 @@
     <t>蓝莓</t>
   </si>
   <si>
-    <t>夏季常见浆果，酸甜小颗，适合搭配酸奶或甜品,平性或偏凉。</t>
-  </si>
-  <si>
     <t>blueberry.jpg</t>
   </si>
   <si>
@@ -557,9 +470,6 @@
     <t>芒果</t>
   </si>
   <si>
-    <t>夏季热带水果，香气浓郁、口感绵甜。偏温，部分人吃多了容易上火。</t>
-  </si>
-  <si>
     <t>mango.jpg</t>
   </si>
   <si>
@@ -572,9 +482,6 @@
     <t>草莓</t>
   </si>
   <si>
-    <t>冬春季常见水果，酸甜清香。</t>
-  </si>
-  <si>
     <t>strawberry.jpg</t>
   </si>
   <si>
@@ -587,9 +494,6 @@
     <t>桃子</t>
   </si>
   <si>
-    <t>夏季水果，果香明显、口感柔软。偏温，适量享用。</t>
-  </si>
-  <si>
     <t>peach.jpg</t>
   </si>
   <si>
@@ -602,9 +506,6 @@
     <t>梨</t>
   </si>
   <si>
-    <t>秋季常见水果，水分足、口感清甜。</t>
-  </si>
-  <si>
     <t>pear.jpg</t>
   </si>
   <si>
@@ -617,9 +518,6 @@
     <t>葡萄</t>
   </si>
   <si>
-    <t>夏秋季水果，酸甜多汁。</t>
-  </si>
-  <si>
     <t>grape.jpg</t>
   </si>
   <si>
@@ -632,12 +530,6 @@
     <t>火龙果</t>
   </si>
   <si>
-    <t>夏秋季常见水果，清甜柔软。</t>
-  </si>
-  <si>
-    <t>dragon-fruit.jpg</t>
-  </si>
-  <si>
     <t>夏秋、偏凉</t>
   </si>
   <si>
@@ -647,9 +539,6 @@
     <t>橙子</t>
   </si>
   <si>
-    <t>秋冬季常见水果，酸甜多汁、香气清新。</t>
-  </si>
-  <si>
     <t>orange.jpg</t>
   </si>
   <si>
@@ -673,17 +562,489 @@
   </si>
   <si>
     <t>10</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>荔枝冰酿</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>空山栀子</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>兰香青柠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>初恋玫瑰青提</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>武汉茉莉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>白兰玉露</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>咸宁桂花</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO YEYE NO TEA02</t>
+  </si>
+  <si>
+    <t>NO YEYE NO TEA03</t>
+  </si>
+  <si>
+    <t>NO YEYE NO TEA04</t>
+  </si>
+  <si>
+    <t>NO YEYE NO TEA05</t>
+  </si>
+  <si>
+    <t>NO YEYE NO TEA06</t>
+  </si>
+  <si>
+    <t>NO YEYE NO TEA07</t>
+  </si>
+  <si>
+    <t>NO YEYE NO TEA08</t>
+  </si>
+  <si>
+    <t>20</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>30</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>三重柠香</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>非遗米酿、经典必喝</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>爷爷不泡茶首创，荔枝的鲜、冰酿的醇与花魁单丛的甘爽，碰撞层层鲜甜。孝感米酿升级，冰凉软的咀嚼惊喜。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>杯型: 大杯、中杯
+温度：少冰（推荐）、去冰、温热
+甜度: 不另外加糖（推荐）、七分糖、五分糖
+小料：茶冻（标准）、去茶冻</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>杯型: 大杯、中杯
 温度：冰（推荐）、温热
-糖度: 七分糖（推荐）、五分糖、三分糖
+甜度: 七分糖（推荐）、五分糖、三分糖
 茶底：含茶底（推荐）、去茶底</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>七窨茉莉花茶融入新鲜蜜桃爆汁果肉。</t>
+    <t>杯型: 大杯、中杯
+温度：少冰（推荐）、热
+甜度: 七分糖（推荐）、五分糖、三分糖、不另外加糖（不推荐）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>三倍奶香、喝栀子</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>杯型: 大杯、中杯
+温度：少冰（推荐）、去冰、热
+甜度: 七分糖（推荐）、全塘、五分糖、三分糖（口感淡）、不另外加糖（口感淡）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>手剥、招牌</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级七套武汉茉莉茶底加入酸甜青提汁，入口果香、花香、茶香犹如清风席卷，看得到的青提果肉与马蹄丸子！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>清冽鲜灵的白兰玉露茶汤融合鲜活青柠，最后撒上青柠皮碎，于绵密中散发清新果香，三重柠香一口感受！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>甄选乐山子，独特天然奶香，福建大白毫与四川毛峰双茶底，栀子与茶比例3:1!入口清新甘甜，回味温润奶香！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>杯型: 大杯、中杯
+温度：少冰（推荐）、少少冰、冰
+甜度: 七分糖（推荐）、五分糖、三分糖
+小料：马蹄丸子（标准）、自然香柚冻</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>七窨茉莉花茶融入新鲜蜜桃爆汁果肉，撞入Q弹的双皮奶和牛奶，满口茉莉清香而不腻，鲜甜爽口。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>七窨茉莉、轻盈奶香</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级后的武汉茉莉茶底，优质双莱莉与云南高山茶底大白毫，轻盈奶香之中又透着高昂茉莉花香。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>恩施玉露、馥郁兰香</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>甄选白兰中上等佳品“建兰”，拼配湖北名茶、恩施城市名片--恩施玉露，经清甜牛奶融合后丝滑入口。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>咸宁，桂花之乡。首配洞庭碧螺春茶，融合牧场牛奶丝滑口感，敢问茶友千年古桂城结的桂花是什么味道?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>桂花之乡、清雅桂香</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO YEYE NO TEA09</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>红苹果</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>90</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>浓郁果香</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>七音茉莉绿茶遇见精选红富士苹果汁，花香茶香果香自然细密交融，搭配醇厚牛奶，顺滑入喉。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>杯型: 大杯、中杯
+温度：少冰（推荐）、去冰、热
+甜度: 三分糖（推荐）、七分糖、五分糖、不另外加糖</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>杯型: 大杯、中杯
+温度：少冰（推荐）、去冰、热
+甜度: 七分糖（推荐）、全糖、五分糖、三分糖（口感淡）、不另外加糖（口感淡）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>breakfast</t>
+  </si>
+  <si>
+    <t>breakfast</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>早餐</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>20</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>30</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>99</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>98</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>breakfast01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>breakfast02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>breakfast03</t>
+  </si>
+  <si>
+    <t>香菇青菜包</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>豆沙包</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>豆腐包</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dessert01.jpg</t>
+  </si>
+  <si>
+    <t>Come_Wanka01.jpg</t>
+  </si>
+  <si>
+    <t>麦当劳</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>肯德基</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿茶餐厅</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>main01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>main02</t>
+  </si>
+  <si>
+    <t>main03</t>
+  </si>
+  <si>
+    <t>main04</t>
+  </si>
+  <si>
+    <t>烤鱼</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>20</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>KFC.jpg</t>
+  </si>
+  <si>
+    <t>McDonald.jpg</t>
+  </si>
+  <si>
+    <t>汉堡、快餐</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GreenTea.jpg</t>
+  </si>
+  <si>
+    <t>浙菜</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoastFish.jpg</t>
+  </si>
+  <si>
+    <t>辣</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>desc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>main05</t>
+  </si>
+  <si>
+    <t>火锅</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>50</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>hotpot.jpg</t>
+  </si>
+  <si>
+    <t>奶茶搭子</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>main06</t>
+  </si>
+  <si>
+    <t>烤肉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>60</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>main07</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>9</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ramen.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛肉拉面</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Baozi01.jpg</t>
+  </si>
+  <si>
+    <t>Tanghulu.jpg</t>
+  </si>
+  <si>
+    <t>dessert02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>糖葫芦</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EggTart.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dessert03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>蛋挞</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>20</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dragon_fruit.jpg</t>
+  </si>
+  <si>
+    <t>fruit11</t>
+  </si>
+  <si>
+    <t>榴莲</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>durian.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fruit12</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>菠萝</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>110</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>pineapple.jpg</t>
+  </si>
+  <si>
+    <t>Barbecue.jpg</t>
+  </si>
+  <si>
+    <t>coconut.jpg</t>
+  </si>
+  <si>
+    <t>fruit13</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>11</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>椰子</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fruit14</t>
+  </si>
+  <si>
+    <t>樱桃</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>55</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>cherry.jpg</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -744,7 +1105,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -767,11 +1128,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE6E1DA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE6E1DA"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -793,6 +1165,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1216,7 +1597,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="22" customWidth="1"/>
@@ -1236,171 +1617,186 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
-        <v>25</v>
+        <v>213</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>27</v>
+        <v>214</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>51</v>
+        <v>44</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>54</v>
+        <v>46</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>57</v>
+        <v>48</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>60</v>
+        <v>50</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>63</v>
+        <v>52</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>66</v>
+        <v>54</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>69</v>
+        <v>56</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:C17" xr:uid="{00000000-0009-0000-0000-000002000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C17">
+      <sortCondition ref="C1:C17"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1408,7 +1804,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1425,10 +1821,10 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>22</v>
@@ -1440,27 +1836,27 @@
         <v>24</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>72</v>
+        <v>254</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
-        <v>77</v>
+        <v>240</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>78</v>
+        <v>237</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>25</v>
@@ -1471,28 +1867,24 @@
       <c r="E2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="F2" s="9"/>
       <c r="G2" s="4" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>81</v>
+        <v>248</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>83</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="J2" s="7"/>
     </row>
     <row r="3" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
-        <v>84</v>
+        <v>241</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>85</v>
+        <v>238</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>25</v>
@@ -1500,686 +1892,1291 @@
       <c r="D3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>86</v>
-      </c>
+      <c r="E3" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="F3" s="9"/>
       <c r="G3" s="4" t="s">
-        <v>80</v>
+        <v>246</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>87</v>
+        <v>247</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>89</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="J3" s="7"/>
     </row>
     <row r="4" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
-        <v>90</v>
+        <v>242</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>91</v>
+        <v>239</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>92</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="F4" s="9"/>
       <c r="G4" s="4" t="s">
-        <v>80</v>
+        <v>246</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I4" s="7"/>
+        <v>250</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>251</v>
+      </c>
       <c r="J4" s="7"/>
     </row>
     <row r="5" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
-        <v>94</v>
+        <v>243</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>95</v>
+        <v>244</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>96</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="9"/>
       <c r="G5" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="H5" s="4"/>
+        <v>65</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>252</v>
+      </c>
       <c r="I5" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>98</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="J5" s="7"/>
     </row>
     <row r="6" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>99</v>
+        <v>255</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>100</v>
+        <v>256</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>101</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="F6" s="9"/>
       <c r="G6" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="H6" s="4"/>
+        <v>257</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>259</v>
+      </c>
       <c r="I6" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>103</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
-        <v>104</v>
+        <v>261</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>105</v>
+        <v>262</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>107</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="F7" s="9"/>
       <c r="G7" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>109</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
     </row>
     <row r="8" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
-        <v>110</v>
+        <v>264</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>111</v>
+        <v>267</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>112</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="F8" s="9"/>
       <c r="G8" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>114</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
     </row>
     <row r="9" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>118</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="F9" s="9"/>
       <c r="G9" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>120</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
-        <v>121</v>
+        <v>270</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>122</v>
+        <v>271</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>124</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="F10" s="9"/>
       <c r="G10" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>126</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
     </row>
     <row r="11" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
-        <v>127</v>
+        <v>274</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>128</v>
+        <v>275</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>130</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="F11" s="9"/>
       <c r="G11" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>132</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
     </row>
     <row r="12" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
-        <v>133</v>
+        <v>229</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>136</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="F12" s="9"/>
       <c r="G12" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>138</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
     </row>
     <row r="13" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
-        <v>139</v>
+        <v>230</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>140</v>
+        <v>233</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>142</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="F13" s="9"/>
       <c r="G13" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>144</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
     </row>
     <row r="14" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
-        <v>145</v>
+        <v>231</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>146</v>
+        <v>234</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>147</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="F14" s="9"/>
       <c r="G14" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>149</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
     </row>
     <row r="15" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>201</v>
+        <v>68</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>204</v>
+        <v>34</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>206</v>
+        <v>70</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="H15" s="4"/>
+        <v>65</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>236</v>
+      </c>
       <c r="I15" s="7" t="s">
-        <v>202</v>
+        <v>71</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>205</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>153</v>
+        <v>236</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="J16" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="17" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>156</v>
+        <v>79</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>158</v>
+        <v>236</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J17" s="7"/>
+        <v>82</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="18" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
-        <v>160</v>
+        <v>84</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>106</v>
+        <v>33</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>162</v>
+        <v>86</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>163</v>
+        <v>236</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="J18" s="7"/>
+        <v>87</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="19" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="4" t="s">
-        <v>165</v>
+        <v>89</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>166</v>
+        <v>90</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>167</v>
+        <v>92</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>168</v>
+        <v>236</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="J19" s="7"/>
+        <v>93</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="20" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="4" t="s">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>171</v>
+        <v>96</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>172</v>
+        <v>98</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>173</v>
+        <v>236</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="J20" s="7"/>
+        <v>99</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="21" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="4" t="s">
-        <v>175</v>
+        <v>101</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>176</v>
+        <v>102</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>177</v>
+        <v>104</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>178</v>
+        <v>236</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="J21" s="7"/>
+        <v>105</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="22" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
-        <v>180</v>
+        <v>107</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>182</v>
+        <v>110</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>183</v>
+        <v>236</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="J22" s="7"/>
+        <v>111</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="23" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
-        <v>185</v>
+        <v>113</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>186</v>
+        <v>114</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>187</v>
+        <v>116</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>188</v>
+        <v>236</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="J23" s="7"/>
+        <v>117</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="24" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="4" t="s">
-        <v>190</v>
+        <v>119</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>191</v>
+        <v>120</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>141</v>
+        <v>36</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>192</v>
+        <v>121</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>193</v>
+        <v>236</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="J24" s="7"/>
+        <v>122</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="25" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>196</v>
+        <v>163</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>167</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>197</v>
       </c>
       <c r="G25" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="H25" s="4"/>
+      <c r="I25" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H26" s="4"/>
+      <c r="I26" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H27" s="4"/>
+      <c r="I27" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H28" s="4"/>
+      <c r="I28" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H29" s="4"/>
+      <c r="I29" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H30" s="4"/>
+      <c r="I30" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H31" s="4"/>
+      <c r="I31" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H32" s="4"/>
+      <c r="I32" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="H33" s="4"/>
+      <c r="I33" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34" s="7"/>
+      <c r="G34" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="J34" s="7"/>
+    </row>
+    <row r="35" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F35" s="7"/>
+      <c r="G35" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="J35" s="7"/>
+    </row>
+    <row r="36" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="H25" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="J25" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="J36" s="7"/>
+    </row>
+    <row r="37" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F37" s="7"/>
+      <c r="G37" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="J37" s="7"/>
+    </row>
+    <row r="38" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F38" s="7"/>
+      <c r="G38" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="J38" s="7"/>
+    </row>
+    <row r="39" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F39" s="7"/>
+      <c r="G39" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="J39" s="7"/>
+    </row>
+    <row r="40" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F40" s="7"/>
+      <c r="G40" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="J40" s="7"/>
+    </row>
+    <row r="41" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F41" s="7"/>
+      <c r="G41" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="J41" s="7"/>
+    </row>
+    <row r="42" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F42" s="7"/>
+      <c r="G42" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="J42" s="7"/>
+    </row>
+    <row r="43" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F43" s="7"/>
+      <c r="G43" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="J43" s="7"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A44" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="F44" s="7"/>
+      <c r="G44" s="4">
+        <v>0</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A45" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="F45" s="7"/>
+      <c r="G45" s="4">
+        <v>0</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A46" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="F46" s="7"/>
+      <c r="G46" s="4">
+        <v>0</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="I46" s="7"/>
+      <c r="J46" s="7"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A47" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="F47" s="7"/>
+      <c r="G47" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J25" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:J43" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/tools/menu-workbook/menu-data.xlsx
+++ b/tools/menu-workbook/menu-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\BackUp\AI+网络项目孵化\Baby_Menu_Applet\tools\menu-workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF86D68-6167-4B7B-BD07-A9CF02A6AF3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{994D827C-73CB-4134-A015-8CD5B9AAAEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Categories!$A$1:$C$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Dishes!$A$1:$J$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Dishes!$A$1:$J$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Shop!$A$1:$G$2</definedName>
   </definedNames>
   <calcPr calcId="181029" forceFullCalc="1"/>
@@ -28,72 +28,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="294">
-  <si>
-    <t>菜单数据维护说明</t>
-  </si>
-  <si>
-    <t>日常主要修改 Shop、Categories、Dishes 三张表。</t>
-  </si>
-  <si>
-    <t>Dishes.categoryName 是公式展示列，会根据 categoryId 自动显示分类名，不需要手动改。</t>
-  </si>
-  <si>
-    <t>Dishes.tags 用顿号或逗号分隔，例如：招牌、推荐。</t>
-  </si>
-  <si>
-    <t>Dishes.options 一行一个规格组，例如：糖度: 七分糖、五分糖。默认必选；可选规格写成：小料(可选): 珍珠、椰果。</t>
-  </si>
-  <si>
-    <t>ID 是稳定引用键。重命名分类或商品时，只改名称列，不要为了改展示名去改 ID。</t>
-  </si>
-  <si>
-    <t>图片只在 Dishes.imageFile 填文件名，例如 mango.jpg；留空会使用占位图。</t>
-  </si>
-  <si>
-    <t>改完后运行：node tools\generate-menu-data.js</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>subtitle</t>
-  </si>
-  <si>
-    <t>shareTitle</t>
-  </si>
-  <si>
-    <t>shareImage</t>
-  </si>
-  <si>
-    <t>pageBackgroundImage</t>
-  </si>
-  <si>
-    <t>headerBackgroundImage</t>
-  </si>
-  <si>
-    <t>headerBackgroundPosition</t>
-  </si>
-  <si>
-    <t>宝宝小厨房</t>
-  </si>
-  <si>
-    <t>小画家宝宝专用菜单</t>
-  </si>
-  <si>
-    <t>漂亮宝宝吃饭饭</t>
-  </si>
-  <si>
-    <t>../../assets/share.jpg</t>
-  </si>
-  <si>
-    <t>../../assets/backgrounds/page-bg.jpg</t>
-  </si>
-  <si>
-    <t>../../assets/backgrounds/header-bg.jpg</t>
-  </si>
-  <si>
-    <t>center 60%</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="384">
+  <si>
+    <t>dishId</t>
+  </si>
+  <si>
+    <t>dishName</t>
   </si>
   <si>
     <t>categoryId</t>
@@ -105,6 +45,27 @@
     <t>order</t>
   </si>
   <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>imageFile</t>
+  </si>
+  <si>
+    <t>tags</t>
+  </si>
+  <si>
+    <t>options</t>
+  </si>
+  <si>
+    <t>main01</t>
+  </si>
+  <si>
+    <t>麦当劳</t>
+  </si>
+  <si>
     <t>main</t>
   </si>
   <si>
@@ -114,22 +75,157 @@
     <t>10</t>
   </si>
   <si>
-    <t>fruit</t>
-  </si>
-  <si>
-    <t>水果</t>
+    <t>0</t>
+  </si>
+  <si>
+    <t>McDonald.jpg</t>
+  </si>
+  <si>
+    <t>汉堡、快餐</t>
+  </si>
+  <si>
+    <t>main02</t>
+  </si>
+  <si>
+    <t>肯德基</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
+    <t>KFC.jpg</t>
+  </si>
+  <si>
+    <t>main03</t>
+  </si>
+  <si>
+    <t>绿茶餐厅</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>GreenTea.jpg</t>
+  </si>
+  <si>
+    <t>浙菜</t>
+  </si>
+  <si>
+    <t>main04</t>
+  </si>
+  <si>
+    <t>烤鱼</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>RoastFish.jpg</t>
+  </si>
+  <si>
+    <t>辣</t>
+  </si>
+  <si>
+    <t>main05</t>
+  </si>
+  <si>
+    <t>火锅</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>hotpot.jpg</t>
+  </si>
+  <si>
+    <t>奶茶搭子</t>
+  </si>
+  <si>
+    <t>main06</t>
+  </si>
+  <si>
+    <t>烤肉</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>Barbecue.jpg</t>
+  </si>
+  <si>
+    <t>main07</t>
+  </si>
+  <si>
+    <t>牛肉拉面</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Ramen.jpg</t>
+  </si>
+  <si>
+    <t>dessert01</t>
+  </si>
+  <si>
+    <t>榴莲千层</t>
+  </si>
+  <si>
     <t>dessert</t>
   </si>
   <si>
     <t>甜品</t>
   </si>
   <si>
-    <t>40</t>
+    <t>dessert01.jpg</t>
+  </si>
+  <si>
+    <t>dessert02</t>
+  </si>
+  <si>
+    <t>糖葫芦</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Tanghulu.jpg</t>
+  </si>
+  <si>
+    <t>dessert03</t>
+  </si>
+  <si>
+    <t>蛋挞</t>
+  </si>
+  <si>
+    <t>EggTart.jpg</t>
+  </si>
+  <si>
+    <t>香菇青菜包</t>
+  </si>
+  <si>
+    <t>breakfast</t>
+  </si>
+  <si>
+    <t>早餐</t>
+  </si>
+  <si>
+    <t>Baozi01.jpg</t>
+  </si>
+  <si>
+    <t>breakfast02</t>
+  </si>
+  <si>
+    <t>豆沙包</t>
+  </si>
+  <si>
+    <t>豆腐包</t>
+  </si>
+  <si>
+    <t>Come Wonka01</t>
+  </si>
+  <si>
+    <t>芒果爽</t>
   </si>
   <si>
     <t>Come Wonka</t>
@@ -138,109 +234,10 @@
     <t>卡旺卡</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>MOLLY TEA</t>
-  </si>
-  <si>
-    <t>茉莉奶白</t>
-  </si>
-  <si>
-    <t>GOOD ME</t>
-  </si>
-  <si>
-    <t>古茗</t>
-  </si>
-  <si>
-    <t>NO YEYE NO TEA</t>
-  </si>
-  <si>
-    <t>爷爷不泡茶</t>
-  </si>
-  <si>
-    <t>HEYTEA</t>
-  </si>
-  <si>
-    <t>喜茶</t>
-  </si>
-  <si>
-    <t>ChaPanda</t>
-  </si>
-  <si>
-    <t>茶百道</t>
-  </si>
-  <si>
-    <t>azcf</t>
-  </si>
-  <si>
-    <t>阿正茶夫</t>
-  </si>
-  <si>
-    <t>A LITTLE TEA</t>
-  </si>
-  <si>
-    <t>一点点</t>
-  </si>
-  <si>
-    <t>NAYUKI</t>
-  </si>
-  <si>
-    <t>奈雪的茶</t>
-  </si>
-  <si>
-    <t>COTTI COFFEE</t>
-  </si>
-  <si>
-    <t>库迪</t>
-  </si>
-  <si>
-    <t>luckin coffee</t>
-  </si>
-  <si>
-    <t>瑞幸</t>
-  </si>
-  <si>
-    <t>AUNTEA JENNY</t>
-  </si>
-  <si>
-    <t>沪上阿姨</t>
-  </si>
-  <si>
-    <t>dishId</t>
-  </si>
-  <si>
-    <t>dishName</t>
-  </si>
-  <si>
-    <t>price</t>
-  </si>
-  <si>
-    <t>imageFile</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>options</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>dessert01</t>
-  </si>
-  <si>
-    <t>榴莲千层</t>
-  </si>
-  <si>
-    <t>Come Wonka01</t>
-  </si>
-  <si>
-    <t>芒果爽</t>
-  </si>
-  <si>
     <t>芒果风味的清爽沙冰饮品，果香明亮，适合作为夏日甜品饮料展示。</t>
+  </si>
+  <si>
+    <t>Come_Wanka01.jpg</t>
   </si>
   <si>
     <t>芒果、沙冰</t>
@@ -276,9 +273,6 @@
     <t>芒果酸奶奶昔</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>芒果果香和酸奶奶昔融合，口感绵密清甜，搭配西米更有咀嚼感。</t>
   </si>
   <si>
@@ -312,9 +306,6 @@
     <t>徽州酒酿</t>
   </si>
   <si>
-    <t>50</t>
-  </si>
-  <si>
     <t>带有酒酿香气的轻沙冰饮品，甜润柔和，搭配马蹄丸子增加口感。</t>
   </si>
   <si>
@@ -330,9 +321,6 @@
   </si>
   <si>
     <t>黑全套奶茶</t>
-  </si>
-  <si>
-    <t>60</t>
   </si>
   <si>
     <t>卡旺卡经典奶茶，搭配黑糖布丁、芋圆和黑米等小料，口感扎实丰富。</t>
@@ -417,6 +405,9 @@
     <t>满杯猕猴桃</t>
   </si>
   <si>
+    <t>100</t>
+  </si>
+  <si>
     <t>猕猴桃果香清爽，酸甜开胃，搭配冰粉带来轻盈顺滑的口感。</t>
   </si>
   <si>
@@ -428,338 +419,749 @@
 冰粉: 标准冰粉、少冰粉、多冰粉、无冰粉</t>
   </si>
   <si>
-    <t>fruit01</t>
-  </si>
-  <si>
-    <t>荔枝</t>
-  </si>
-  <si>
-    <t>lychee.jpg</t>
-  </si>
-  <si>
-    <t>夏季、偏温热、易上火</t>
-  </si>
-  <si>
-    <t>fruit02</t>
-  </si>
-  <si>
-    <t>西瓜</t>
-  </si>
-  <si>
-    <t>watermelon.jpg</t>
-  </si>
-  <si>
-    <t>夏季、寒凉、清爽</t>
-  </si>
-  <si>
-    <t>fruit03</t>
-  </si>
-  <si>
-    <t>蓝莓</t>
-  </si>
-  <si>
-    <t>blueberry.jpg</t>
-  </si>
-  <si>
-    <t>夏季、平性、酸甜</t>
-  </si>
-  <si>
-    <t>fruit04</t>
-  </si>
-  <si>
-    <t>芒果</t>
-  </si>
-  <si>
-    <t>mango.jpg</t>
-  </si>
-  <si>
-    <t>夏季、偏温、易上火</t>
-  </si>
-  <si>
-    <t>fruit05</t>
-  </si>
-  <si>
-    <t>草莓</t>
-  </si>
-  <si>
-    <t>strawberry.jpg</t>
-  </si>
-  <si>
-    <t>冬春、偏凉、酸甜</t>
-  </si>
-  <si>
-    <t>fruit06</t>
-  </si>
-  <si>
-    <t>桃子</t>
-  </si>
-  <si>
-    <t>peach.jpg</t>
-  </si>
-  <si>
-    <t>夏季、偏温</t>
-  </si>
-  <si>
-    <t>fruit07</t>
-  </si>
-  <si>
-    <t>梨</t>
-  </si>
-  <si>
-    <t>pear.jpg</t>
-  </si>
-  <si>
-    <t>秋季、偏凉、清润</t>
-  </si>
-  <si>
-    <t>fruit08</t>
-  </si>
-  <si>
-    <t>葡萄</t>
-  </si>
-  <si>
-    <t>grape.jpg</t>
-  </si>
-  <si>
-    <t>夏秋、平性</t>
-  </si>
-  <si>
-    <t>fruit09</t>
-  </si>
-  <si>
-    <t>火龙果</t>
-  </si>
-  <si>
-    <t>夏秋、偏凉</t>
-  </si>
-  <si>
-    <t>fruit10</t>
-  </si>
-  <si>
-    <t>橙子</t>
-  </si>
-  <si>
-    <t>orange.jpg</t>
-  </si>
-  <si>
-    <t>秋冬、偏凉</t>
+    <t>MOLLY TEA01</t>
+  </si>
+  <si>
+    <t>开心果茉莉椰</t>
+  </si>
+  <si>
+    <t>MOLLY TEA</t>
+  </si>
+  <si>
+    <t>茉莉奶白</t>
+  </si>
+  <si>
+    <t>MOLLY TEA02</t>
+  </si>
+  <si>
+    <t>MOLLY TEA03</t>
+  </si>
+  <si>
+    <t>栀子奶白</t>
+  </si>
+  <si>
+    <t>MOLLY TEA04</t>
+  </si>
+  <si>
+    <t>白兰</t>
+  </si>
+  <si>
+    <t>MOLLY TEA05</t>
+  </si>
+  <si>
+    <t>抹茶白兰</t>
+  </si>
+  <si>
+    <t>MOLLY TEA06</t>
+  </si>
+  <si>
+    <t>栀子冰茶</t>
+  </si>
+  <si>
+    <t>MOLLY TEA07</t>
+  </si>
+  <si>
+    <t>针王苹果</t>
+  </si>
+  <si>
+    <t>MOLLY TEA08</t>
+  </si>
+  <si>
+    <t>针王葡萄</t>
+  </si>
+  <si>
+    <t>MOLLY TEA09</t>
+  </si>
+  <si>
+    <t>抹茶针王</t>
+  </si>
+  <si>
+    <t>MOLLY TEA10</t>
+  </si>
+  <si>
+    <t>茉莉针王</t>
+  </si>
+  <si>
+    <t>MOLLY TEA11</t>
+  </si>
+  <si>
+    <t>针王冰茶</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>MOLLY TEA12</t>
+  </si>
+  <si>
+    <t>茉莉椰冰茶</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>MOLLY TEA13</t>
+  </si>
+  <si>
+    <t>130</t>
   </si>
   <si>
     <t>NO YEYE NO TEA01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>桃桃双皮奶</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO YEYE NO TEA</t>
+  </si>
+  <si>
+    <t>爷爷不泡茶</t>
+  </si>
+  <si>
+    <t>七窨茉莉花茶融入新鲜蜜桃爆汁果肉，撞入Q弹的双皮奶和牛奶，满口茉莉清香而不腻，鲜甜爽口。</t>
   </si>
   <si>
     <t>Q弹奶冻、清甜蜜桃</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>10</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>杯型: 大杯、中杯
+温度：冰（推荐）、温热
+甜度: 七分糖（推荐）、五分糖、三分糖
+茶底：含茶底（推荐）、去茶底</t>
+  </si>
+  <si>
+    <t>NO YEYE NO TEA02</t>
   </si>
   <si>
     <t>荔枝冰酿</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>空山栀子</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>兰香青柠</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>初恋玫瑰青提</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>武汉茉莉</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>白兰玉露</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>咸宁桂花</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>NO YEYE NO TEA02</t>
-  </si>
-  <si>
-    <t>NO YEYE NO TEA03</t>
-  </si>
-  <si>
-    <t>NO YEYE NO TEA04</t>
-  </si>
-  <si>
-    <t>NO YEYE NO TEA05</t>
-  </si>
-  <si>
-    <t>NO YEYE NO TEA06</t>
-  </si>
-  <si>
-    <t>NO YEYE NO TEA07</t>
-  </si>
-  <si>
-    <t>NO YEYE NO TEA08</t>
-  </si>
-  <si>
-    <t>20</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>30</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>三重柠香</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>爷爷不泡茶首创，荔枝的鲜、冰酿的醇与花魁单丛的甘爽，碰撞层层鲜甜。孝感米酿升级，冰凉软的咀嚼惊喜。</t>
   </si>
   <si>
     <t>非遗米酿、经典必喝</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>爷爷不泡茶首创，荔枝的鲜、冰酿的醇与花魁单丛的甘爽，碰撞层层鲜甜。孝感米酿升级，冰凉软的咀嚼惊喜。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>杯型: 大杯、中杯
 温度：少冰（推荐）、去冰、温热
 甜度: 不另外加糖（推荐）、七分糖、五分糖
 小料：茶冻（标准）、去茶冻</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO YEYE NO TEA03</t>
+  </si>
+  <si>
+    <t>空山栀子</t>
+  </si>
+  <si>
+    <t>甄选乐山子，独特天然奶香，福建大白毫与四川毛峰双茶底，栀子与茶比例3:1!入口清新甘甜，回味温润奶香！</t>
+  </si>
+  <si>
+    <t>三倍奶香、喝栀子</t>
   </si>
   <si>
     <t>杯型: 大杯、中杯
-温度：冰（推荐）、温热
-甜度: 七分糖（推荐）、五分糖、三分糖
-茶底：含茶底（推荐）、去茶底</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+温度：少冰（推荐）、去冰、热
+甜度: 七分糖（推荐）、全塘、五分糖、三分糖（口感淡）、不另外加糖（口感淡）</t>
+  </si>
+  <si>
+    <t>NO YEYE NO TEA04</t>
+  </si>
+  <si>
+    <t>兰香青柠</t>
+  </si>
+  <si>
+    <t>清冽鲜灵的白兰玉露茶汤融合鲜活青柠，最后撒上青柠皮碎，于绵密中散发清新果香，三重柠香一口感受！</t>
+  </si>
+  <si>
+    <t>三重柠香</t>
   </si>
   <si>
     <t>杯型: 大杯、中杯
 温度：少冰（推荐）、热
 甜度: 七分糖（推荐）、五分糖、三分糖、不另外加糖（不推荐）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>三倍奶香、喝栀子</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>杯型: 大杯、中杯
-温度：少冰（推荐）、去冰、热
-甜度: 七分糖（推荐）、全塘、五分糖、三分糖（口感淡）、不另外加糖（口感淡）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO YEYE NO TEA05</t>
+  </si>
+  <si>
+    <t>初恋玫瑰青提</t>
+  </si>
+  <si>
+    <t>升级七套武汉茉莉茶底加入酸甜青提汁，入口果香、花香、茶香犹如清风席卷，看得到的青提果肉与马蹄丸子！</t>
   </si>
   <si>
     <t>手剥、招牌</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>升级七套武汉茉莉茶底加入酸甜青提汁，入口果香、花香、茶香犹如清风席卷，看得到的青提果肉与马蹄丸子！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>清冽鲜灵的白兰玉露茶汤融合鲜活青柠，最后撒上青柠皮碎，于绵密中散发清新果香，三重柠香一口感受！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>甄选乐山子，独特天然奶香，福建大白毫与四川毛峰双茶底，栀子与茶比例3:1!入口清新甘甜，回味温润奶香！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>杯型: 大杯、中杯
 温度：少冰（推荐）、少少冰、冰
 甜度: 七分糖（推荐）、五分糖、三分糖
 小料：马蹄丸子（标准）、自然香柚冻</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>七窨茉莉花茶融入新鲜蜜桃爆汁果肉，撞入Q弹的双皮奶和牛奶，满口茉莉清香而不腻，鲜甜爽口。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO YEYE NO TEA06</t>
+  </si>
+  <si>
+    <t>武汉茉莉</t>
+  </si>
+  <si>
+    <t>升级后的武汉茉莉茶底，优质双莱莉与云南高山茶底大白毫，轻盈奶香之中又透着高昂茉莉花香。</t>
   </si>
   <si>
     <t>七窨茉莉、轻盈奶香</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>升级后的武汉茉莉茶底，优质双莱莉与云南高山茶底大白毫，轻盈奶香之中又透着高昂茉莉花香。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>杯型: 大杯、中杯
+温度：少冰（推荐）、去冰、热
+甜度: 七分糖（推荐）、全糖、五分糖、三分糖（口感淡）、不另外加糖（口感淡）</t>
+  </si>
+  <si>
+    <t>NO YEYE NO TEA07</t>
+  </si>
+  <si>
+    <t>白兰玉露</t>
+  </si>
+  <si>
+    <t>甄选白兰中上等佳品“建兰”，拼配湖北名茶、恩施城市名片--恩施玉露，经清甜牛奶融合后丝滑入口。</t>
   </si>
   <si>
     <t>恩施玉露、馥郁兰香</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>甄选白兰中上等佳品“建兰”，拼配湖北名茶、恩施城市名片--恩施玉露，经清甜牛奶融合后丝滑入口。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO YEYE NO TEA08</t>
+  </si>
+  <si>
+    <t>咸宁桂花</t>
   </si>
   <si>
     <t>咸宁，桂花之乡。首配洞庭碧螺春茶，融合牧场牛奶丝滑口感，敢问茶友千年古桂城结的桂花是什么味道?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>桂花之乡、清雅桂香</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>NO YEYE NO TEA09</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>红苹果</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>90</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>七音茉莉绿茶遇见精选红富士苹果汁，花香茶香果香自然细密交融，搭配醇厚牛奶，顺滑入喉。</t>
   </si>
   <si>
     <t>浓郁果香</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>七音茉莉绿茶遇见精选红富士苹果汁，花香茶香果香自然细密交融，搭配醇厚牛奶，顺滑入喉。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>杯型: 大杯、中杯
 温度：少冰（推荐）、去冰、热
 甜度: 三分糖（推荐）、七分糖、五分糖、不另外加糖</t>
+  </si>
+  <si>
+    <t>fruit01</t>
+  </si>
+  <si>
+    <t>荔枝</t>
+  </si>
+  <si>
+    <t>fruit</t>
+  </si>
+  <si>
+    <t>水果</t>
+  </si>
+  <si>
+    <t>lychee.jpg</t>
+  </si>
+  <si>
+    <t>夏季、偏温热、易上火</t>
+  </si>
+  <si>
+    <t>fruit02</t>
+  </si>
+  <si>
+    <t>西瓜</t>
+  </si>
+  <si>
+    <t>watermelon.jpg</t>
+  </si>
+  <si>
+    <t>夏季、寒凉、下火</t>
+  </si>
+  <si>
+    <t>fruit03</t>
+  </si>
+  <si>
+    <t>蓝莓</t>
+  </si>
+  <si>
+    <t>blueberry.jpg</t>
+  </si>
+  <si>
+    <t>夏季、平性、不易上火</t>
+  </si>
+  <si>
+    <t>fruit04</t>
+  </si>
+  <si>
+    <t>芒果</t>
+  </si>
+  <si>
+    <t>mango.jpg</t>
+  </si>
+  <si>
+    <t>夏季、偏温、易上火</t>
+  </si>
+  <si>
+    <t>fruit05</t>
+  </si>
+  <si>
+    <t>草莓</t>
+  </si>
+  <si>
+    <t>strawberry.jpg</t>
+  </si>
+  <si>
+    <t>冬春、偏凉、下火</t>
+  </si>
+  <si>
+    <t>fruit06</t>
+  </si>
+  <si>
+    <t>桃子</t>
+  </si>
+  <si>
+    <t>peach.jpg</t>
+  </si>
+  <si>
+    <t>fruit07</t>
+  </si>
+  <si>
+    <t>梨</t>
+  </si>
+  <si>
+    <t>pear.jpg</t>
+  </si>
+  <si>
+    <t>秋季、偏凉、下火</t>
+  </si>
+  <si>
+    <t>fruit08</t>
+  </si>
+  <si>
+    <t>葡萄</t>
+  </si>
+  <si>
+    <t>grape.jpg</t>
+  </si>
+  <si>
+    <t>夏秋、平性、不易上火</t>
+  </si>
+  <si>
+    <t>fruit09</t>
+  </si>
+  <si>
+    <t>火龙果</t>
+  </si>
+  <si>
+    <t>dragon_fruit.jpg</t>
+  </si>
+  <si>
+    <t>夏秋、偏凉、下火</t>
+  </si>
+  <si>
+    <t>fruit10</t>
+  </si>
+  <si>
+    <t>橙子</t>
+  </si>
+  <si>
+    <t>orange.jpg</t>
+  </si>
+  <si>
+    <t>秋冬、偏凉、下火</t>
+  </si>
+  <si>
+    <t>fruit11</t>
+  </si>
+  <si>
+    <t>榴莲</t>
+  </si>
+  <si>
+    <t>durian.jpg</t>
+  </si>
+  <si>
+    <t>夏季、热性、易上火</t>
+  </si>
+  <si>
+    <t>fruit12</t>
+  </si>
+  <si>
+    <t>菠萝</t>
+  </si>
+  <si>
+    <t>pineapple.jpg</t>
+  </si>
+  <si>
+    <t>春夏、平性、不易上火</t>
+  </si>
+  <si>
+    <t>fruit13</t>
+  </si>
+  <si>
+    <t>椰子</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>coconut.jpg</t>
+  </si>
+  <si>
+    <t>夏季、偏凉、下火</t>
+  </si>
+  <si>
+    <t>fruit14</t>
+  </si>
+  <si>
+    <t>樱桃</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>cherry.jpg</t>
+  </si>
+  <si>
+    <t>春夏、温性、易上火</t>
+  </si>
+  <si>
+    <t>菜单数据维护说明</t>
+  </si>
+  <si>
+    <t>日常主要修改 Shop、Categories、Dishes 三张表。</t>
+  </si>
+  <si>
+    <t>Dishes.categoryName 是公式展示列，会根据 categoryId 自动显示分类名，不需要手动改。</t>
+  </si>
+  <si>
+    <t>Dishes.tags 用顿号或逗号分隔，例如：招牌、推荐。</t>
+  </si>
+  <si>
+    <t>Dishes.options 一行一个规格组，例如：糖度: 七分糖、五分糖。默认必选；可选规格写成：小料(可选): 珍珠、椰果。</t>
+  </si>
+  <si>
+    <t>ID 是稳定引用键。重命名分类或商品时，只改名称列，不要为了改展示名去改 ID。</t>
+  </si>
+  <si>
+    <t>图片只在 Dishes.imageFile 填文件名，例如 mango.jpg；留空会使用占位图。</t>
+  </si>
+  <si>
+    <t>改完后运行：node tools\generate-menu-data.js</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>subtitle</t>
+  </si>
+  <si>
+    <t>shareTitle</t>
+  </si>
+  <si>
+    <t>shareImage</t>
+  </si>
+  <si>
+    <t>pageBackgroundImage</t>
+  </si>
+  <si>
+    <t>headerBackgroundImage</t>
+  </si>
+  <si>
+    <t>headerBackgroundPosition</t>
+  </si>
+  <si>
+    <t>宝宝小厨房</t>
+  </si>
+  <si>
+    <t>小画家宝宝专用菜单</t>
+  </si>
+  <si>
+    <t>漂亮宝宝吃饭饭</t>
+  </si>
+  <si>
+    <t>../../assets/share.jpg</t>
+  </si>
+  <si>
+    <t>../../assets/backgrounds/page-bg.jpg</t>
+  </si>
+  <si>
+    <t>../../assets/backgrounds/header-bg.jpg</t>
+  </si>
+  <si>
+    <t>center 60%</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>GOOD ME</t>
+  </si>
+  <si>
+    <t>古茗</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>HEYTEA</t>
+  </si>
+  <si>
+    <t>喜茶</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>ChaPanda</t>
+  </si>
+  <si>
+    <t>茶百道</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>azcf</t>
+  </si>
+  <si>
+    <t>阿正茶夫</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>A LITTLE TEA</t>
+  </si>
+  <si>
+    <t>一点点</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>NAYUKI</t>
+  </si>
+  <si>
+    <t>奈雪的茶</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>COTTI COFFEE</t>
+  </si>
+  <si>
+    <t>库迪</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>luckin coffee</t>
+  </si>
+  <si>
+    <t>瑞幸</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>AUNTEA JENNY</t>
+  </si>
+  <si>
+    <t>沪上阿姨</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>无花果碎+茉莉针王+泰国椰皇水+开心果芝士建议不使用吸管，直接饮用体验更佳。</t>
+  </si>
+  <si>
+    <t>椰香升级</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>杯型: 中杯
+温度: 正常冰（推荐）、少冰
+甜度: 正常糖、七分糖、五分糖（推荐）、三分糖、不另外加糖</t>
+  </si>
+  <si>
+    <t>杯型: 中杯
+温度: 正常冰（推荐）、少冰
+甜度: 正常糖、七分糖、五分糖（推荐）、三分糖、不另外加糖</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>茉莉龙芽+牛奶，搭配优质牛乳，甘醇鲜爽、香气悠长。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>五斤栀子一斤茶，五倍栀香入茶，张扬释香。含:栀香绿茶+牛奶。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>杯型: 大杯、中杯
-温度：少冰（推荐）、去冰、热
-甜度: 七分糖（推荐）、全糖、五分糖、三分糖（口感淡）、不另外加糖（口感淡）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>breakfast</t>
-  </si>
-  <si>
-    <t>breakfast</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>早餐</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+温度: 正常冰、少冰（推荐）、去冰（8分满）、热饮
+甜度: 正常糖、七分糖（推荐）、五分糖、三分糖、不另外加糖</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>前调清竹叶香，中调清雅梨子香，尾调栗香熟乳香。含:兰香甘露+牛奶，热饮推荐五分糖。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>招牌、可选热饮</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可选热饮</t>
+  </si>
+  <si>
+    <t>甄选抹茶粉及安佳奶油，现调抹茶芝士绵密柔滑。含:抹茶芝士+兰香甘露+牛奶。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>杯型: 中杯
+温度: 正常冰、少冰（推荐）、去冰、热饮
+甜度: 正常糖、七分糖（推荐）、五分糖、三分糖、不另外加糖</t>
+  </si>
+  <si>
+    <t>杯型: 中杯
+温度: 正常冰、少冰（推荐）、去冰、热饮
+甜度: 正常糖、七分糖（推荐）、五分糖、三分糖、不另外加糖</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>开心小兰花</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>兰香甘露融合海南椰子水，添加浓郁开心果芝士。含:兰香甘露+香椰水+开心果芝士+无花果碎。</t>
+  </si>
+  <si>
+    <t>推荐</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>原创</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>甄选苹果汁，饱含充盈汁水的郁果香，融入高等级的茉莉针王，含:莱莉针王+红苹果汁+牛奶。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>杯型: 中杯、大杯（纸杯出品）
+温度: 正常冰、少冰（推荐）、热
+甜度: 正常糖、七分糖（推荐）、五分糖、三分糖、不另外加糖</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>沁甜馥郁的夏黑葡萄汁，融入七窨茉莉针王，再与醇滑牛乳相遇，含:夏黑葡萄汁+茉莉针王+牛奶。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>杯型: 中杯、大杯（纸杯出品）
+温度: 正常冰（推荐）、少冰、热
+甜度: 正常糖、七分糖（推荐）、五分糖、三分糖、不另外加糖（不推荐）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>甄选抹茶粉及安佳奶油，现调抹茶芝士绵密柔滑。含:抹茶芝士+茉莉针王+牛奶。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>全新升级</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>中国茶叶流通协会认证金奖茉莉茶底!采用等级更高的茉莉针王为茶底，含:茉莉针王+牛奶</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>金奖茉莉、可做热饮</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯茶生香</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>杯型: 中杯
+温度: 正常冰（推荐）、少冰、去冰
+甜度: 正常糖、七分糖（推荐）、五分糖、三分糖、不另外加糖</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>高等级的茉莉针王，前调茉莉花香，中调嫩香毫香显露，尾调冰糖感微甜。含:茉莉针王。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>采用高等级的茉莉针王，搭配泰国香椰水，含:茉莉针王+香椰水。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>杯型: 中杯
+温度: 正常冰、少冰（推荐）、去冰（9分满）
+甜度: 正常糖、七分糖（推荐）、五分糖、三分糖、不另外加糖</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>栀子系列茶底新升级，五斤栀子窨一斤茶，五倍香入茶。尾调干净鲜灵。含:栀香绿茶。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fruit15</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>香蕉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>banana.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>65</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MollyTea01.jpg</t>
+  </si>
+  <si>
+    <t>GOOD ME</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GOOD ME01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GOOD ME02</t>
+  </si>
+  <si>
+    <t>GOOD ME03</t>
+  </si>
+  <si>
+    <t>GOOD ME04</t>
+  </si>
+  <si>
+    <t>GOOD ME05</t>
   </si>
   <si>
     <t>10</t>
@@ -774,277 +1176,154 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>99</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>98</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>88</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>97</t>
+    <t>40</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>50</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云岭茉莉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>冷链鲜奶</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>规格: 中杯、大杯
+温度: 少冰（推荐）、温、热、去冰
+选糖：默认糖
+甜度: 七分甜（推荐）、五分甜、三分甜、十分甜、不另外加糖（不推荐）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云深幽兰</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>锡兰高山红茶</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>规格: 中杯
+去料：去坚果碎
+温度: 少冰（推荐）、温、热
+选糖：默认糖
+甜度: 七分甜（推荐）、五分甜、三分甜、十分甜、不另外加糖（不推荐）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲜打香草籽奶芙顶，奶芙受热易化。茶底以产自斯里兰卡的锡兰红茶为主，拼配中国云南及印度红茶。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>广西横州七窨茉莉花茶。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>超A芝士桃桃</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>规格: 中杯、大杯
+加料：桃桃果茸、多肉、椰果、西米、西柚粒
+温度: 沙冰（推荐）
+选糖：默认糖
+甜度: 七分甜（推荐）、五分甜、十分甜、不另外加糖</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>时令水蜜桃+桃汁+芝士奶盖+Q弹多肉+四季春乌龙，鲜活风味，严选龙泉驿等时令产区水蜜桃。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>手剥现捣、Q弹多肉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>超A多肉葡萄</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>现剥葡萄果肉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>现剥时令葡萄，搭配清冽茉莉花茶与Q弹多肉小料。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>规格: 大杯
+加料：椰果、芦荟、粉宝石、葡萄鲜果肉、西柚粒
+温度: 少冰（推荐）
+选糖：默认糖
+甜度: 七分甜（推荐）、五分甜、三分甜、十分甜、不另外加糖</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>超A芝士葡萄</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>果茶销冠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>现剥葡萄果肉+茉莉花茶+葡萄汁+芝士奶盖+多肉。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>馄饨</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>规格: 小份、大份
+馄饨馅：荠菜、三鲜、猪肉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>breakfast01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>breakfast02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>breakfast04</t>
   </si>
   <si>
     <t>breakfast03</t>
-  </si>
-  <si>
-    <t>香菇青菜包</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>豆沙包</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>豆腐包</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dessert01.jpg</t>
-  </si>
-  <si>
-    <t>Come_Wanka01.jpg</t>
-  </si>
-  <si>
-    <t>麦当劳</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>肯德基</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>绿茶餐厅</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>main01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>main02</t>
-  </si>
-  <si>
-    <t>main03</t>
-  </si>
-  <si>
-    <t>main04</t>
-  </si>
-  <si>
-    <t>烤鱼</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>20</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>KFC.jpg</t>
-  </si>
-  <si>
-    <t>McDonald.jpg</t>
-  </si>
-  <si>
-    <t>汉堡、快餐</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>GreenTea.jpg</t>
-  </si>
-  <si>
-    <t>浙菜</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>RoastFish.jpg</t>
-  </si>
-  <si>
-    <t>辣</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>desc</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>main05</t>
-  </si>
-  <si>
-    <t>火锅</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>50</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>hotpot.jpg</t>
-  </si>
-  <si>
-    <t>奶茶搭子</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>main06</t>
-  </si>
-  <si>
-    <t>烤肉</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>60</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>main07</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>9</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ramen.jpg</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>牛肉拉面</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Baozi01.jpg</t>
-  </si>
-  <si>
-    <t>Tanghulu.jpg</t>
-  </si>
-  <si>
-    <t>dessert02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>糖葫芦</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>6</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EggTart.jpg</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dessert03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>蛋挞</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>20</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dragon_fruit.jpg</t>
-  </si>
-  <si>
-    <t>fruit11</t>
-  </si>
-  <si>
-    <t>榴莲</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>durian.jpg</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>fruit12</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>菠萝</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>110</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>pineapple.jpg</t>
-  </si>
-  <si>
-    <t>Barbecue.jpg</t>
-  </si>
-  <si>
-    <t>coconut.jpg</t>
-  </si>
-  <si>
-    <t>fruit13</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>11</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>椰子</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>fruit14</t>
-  </si>
-  <si>
-    <t>樱桃</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>55</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>cherry.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>breakfast05</t>
+  </si>
+  <si>
+    <t>水饺</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>规格: 小份、大份
+水饺馅：荠菜、三鲜、猪肉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MilkTea04.jpg</t>
+  </si>
+  <si>
+    <t>MilkTea04.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MilkTea03.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>辣度: 不辣、微辣
+香菜：多香菜、少香菜、不要香菜</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1143,7 +1422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1176,6 +1455,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1484,44 +1767,44 @@
     <col min="1" max="1" width="118" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>1</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -1544,48 +1827,48 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>9</v>
+        <v>263</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>10</v>
+        <v>264</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>11</v>
+        <v>265</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>12</v>
+        <v>266</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>13</v>
+        <v>267</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>14</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
-        <v>15</v>
+        <v>269</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>16</v>
+        <v>270</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>17</v>
+        <v>271</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>19</v>
+        <v>273</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>20</v>
+        <v>274</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>21</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -1606,189 +1889,189 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
-        <v>213</v>
+        <v>58</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>214</v>
+        <v>59</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>215</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>216</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
-        <v>28</v>
+        <v>197</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>29</v>
+        <v>198</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>220</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>221</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
-        <v>39</v>
+        <v>278</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>40</v>
+        <v>279</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
-        <v>41</v>
+        <v>152</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>42</v>
+        <v>153</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>222</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
-        <v>43</v>
+        <v>281</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>44</v>
+        <v>282</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>223</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
-        <v>45</v>
+        <v>284</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>46</v>
+        <v>285</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>224</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
-        <v>47</v>
+        <v>287</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>48</v>
+        <v>288</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>225</v>
+        <v>289</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
-        <v>49</v>
+        <v>290</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>50</v>
+        <v>291</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>226</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
-        <v>51</v>
+        <v>293</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>52</v>
+        <v>294</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>227</v>
+        <v>295</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
-        <v>53</v>
+        <v>296</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>54</v>
+        <v>297</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>228</v>
+        <v>298</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
-        <v>55</v>
+        <v>299</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>56</v>
+        <v>300</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>219</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
-        <v>57</v>
+        <v>302</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>58</v>
+        <v>303</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>218</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -1804,14 +2087,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="48" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
@@ -1821,1360 +2104,2039 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>254</v>
+        <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>237</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>248</v>
+        <v>16</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>249</v>
+        <v>17</v>
       </c>
       <c r="J2" s="7"/>
     </row>
     <row r="3" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
-        <v>241</v>
+        <v>18</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>238</v>
+        <v>19</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>245</v>
+        <v>20</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="4" t="s">
-        <v>246</v>
+        <v>15</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>247</v>
+        <v>21</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>249</v>
+        <v>17</v>
       </c>
       <c r="J3" s="7"/>
     </row>
     <row r="4" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
-        <v>242</v>
+        <v>22</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>239</v>
+        <v>23</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="4" t="s">
-        <v>246</v>
+        <v>15</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>250</v>
+        <v>25</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>251</v>
+        <v>26</v>
       </c>
       <c r="J4" s="7"/>
     </row>
     <row r="5" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>244</v>
+        <v>28</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>252</v>
+        <v>30</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>253</v>
+        <v>31</v>
       </c>
       <c r="J5" s="7"/>
     </row>
     <row r="6" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>255</v>
+        <v>32</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>256</v>
+        <v>33</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>258</v>
+        <v>34</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="4" t="s">
-        <v>257</v>
+        <v>15</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>259</v>
+        <v>35</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>260</v>
+        <v>36</v>
       </c>
       <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
-        <v>261</v>
+        <v>37</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>262</v>
+        <v>38</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>263</v>
+        <v>39</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="4" t="s">
-        <v>257</v>
+        <v>15</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>285</v>
+        <v>40</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
     </row>
     <row r="8" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
-        <v>264</v>
+        <v>41</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>267</v>
+        <v>42</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>265</v>
+        <v>43</v>
       </c>
       <c r="F8" s="9"/>
       <c r="G8" s="4" t="s">
-        <v>257</v>
+        <v>15</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>266</v>
+        <v>44</v>
       </c>
       <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
+      <c r="J8" s="7" t="s">
+        <v>383</v>
+      </c>
     </row>
     <row r="9" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F9" s="9"/>
       <c r="G9" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>235</v>
+        <v>49</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
-        <v>270</v>
+        <v>50</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>271</v>
+        <v>51</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>272</v>
+        <v>52</v>
       </c>
       <c r="F10" s="9"/>
       <c r="G10" s="4" t="s">
-        <v>257</v>
+        <v>15</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>269</v>
+        <v>53</v>
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
     </row>
     <row r="11" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
-        <v>274</v>
+        <v>54</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>275</v>
+        <v>55</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>276</v>
+        <v>20</v>
       </c>
       <c r="F11" s="9"/>
       <c r="G11" s="4" t="s">
-        <v>257</v>
+        <v>15</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>273</v>
+        <v>56</v>
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
     <row r="12" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
-        <v>229</v>
+        <v>374</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>232</v>
+        <v>57</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>212</v>
+        <v>58</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>214</v>
+        <v>59</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>215</v>
+        <v>14</v>
       </c>
       <c r="F12" s="9"/>
       <c r="G12" s="4" t="s">
-        <v>65</v>
+        <v>372</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>268</v>
+        <v>60</v>
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
     </row>
     <row r="13" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
-        <v>230</v>
+        <v>61</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>233</v>
+        <v>62</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>212</v>
+        <v>58</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>214</v>
+        <v>59</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>216</v>
+        <v>20</v>
       </c>
       <c r="F13" s="9"/>
       <c r="G13" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>268</v>
+        <v>60</v>
       </c>
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
     </row>
     <row r="14" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
-        <v>231</v>
+        <v>376</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>234</v>
+        <v>63</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>212</v>
+        <v>58</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>214</v>
+        <v>59</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="F14" s="9"/>
       <c r="G14" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>268</v>
+        <v>60</v>
       </c>
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
     </row>
     <row r="15" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
-        <v>68</v>
+        <v>375</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>69</v>
+        <v>371</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>70</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="9"/>
       <c r="G15" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>71</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H15" s="4"/>
+      <c r="I15" s="7"/>
       <c r="J15" s="7" t="s">
-        <v>72</v>
+        <v>373</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
-        <v>73</v>
+        <v>377</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>74</v>
+        <v>378</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>75</v>
-      </c>
+      <c r="F16" s="9"/>
       <c r="G16" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>76</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H16" s="4"/>
+      <c r="I16" s="7"/>
       <c r="J16" s="7" t="s">
-        <v>77</v>
+        <v>379</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>236</v>
+        <v>69</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>236</v>
+        <v>69</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="4" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>236</v>
+        <v>69</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="4" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>236</v>
+        <v>69</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="4" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>103</v>
-      </c>
       <c r="F21" s="7" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>236</v>
+        <v>69</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>109</v>
+        <v>39</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>236</v>
+        <v>69</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>236</v>
+        <v>69</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="4" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>236</v>
+        <v>69</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>164</v>
+        <v>109</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>167</v>
+        <v>66</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>197</v>
+        <v>112</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="H25" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="I25" s="7" t="s">
-        <v>165</v>
+        <v>113</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>188</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>168</v>
+        <v>115</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>116</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>182</v>
+        <v>66</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>186</v>
+        <v>118</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H26" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="I26" s="7" t="s">
-        <v>185</v>
+        <v>119</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>187</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>169</v>
+        <v>121</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>122</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>183</v>
+        <v>123</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>14</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>195</v>
+        <v>305</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H27" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>340</v>
+      </c>
       <c r="I27" s="7" t="s">
-        <v>190</v>
+        <v>306</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>191</v>
+        <v>308</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>170</v>
+        <v>125</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>124</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>33</v>
+        <v>123</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>194</v>
+        <v>309</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H28" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>340</v>
+      </c>
       <c r="I28" s="7" t="s">
-        <v>184</v>
+        <v>313</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>189</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>171</v>
+        <v>126</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>127</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>91</v>
+        <v>123</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>24</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>193</v>
+        <v>310</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H29" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>340</v>
+      </c>
       <c r="I29" s="7" t="s">
-        <v>192</v>
+        <v>314</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>196</v>
+        <v>311</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>172</v>
+        <v>128</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>129</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>97</v>
+        <v>123</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>199</v>
+        <v>312</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H30" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>340</v>
+      </c>
       <c r="I30" s="7" t="s">
-        <v>198</v>
+        <v>314</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>211</v>
+        <v>311</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>173</v>
+        <v>130</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>131</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>103</v>
+        <v>123</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>34</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>201</v>
+        <v>315</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H31" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>340</v>
+      </c>
       <c r="I31" s="7" t="s">
-        <v>200</v>
+        <v>314</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>211</v>
+        <v>317</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>174</v>
+        <v>132</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>318</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>109</v>
+        <v>123</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>202</v>
+        <v>319</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H32" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>340</v>
+      </c>
       <c r="I32" s="7" t="s">
-        <v>203</v>
+        <v>320</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>211</v>
+        <v>307</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>205</v>
+        <v>134</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>206</v>
+        <v>123</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>208</v>
+        <v>322</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="H33" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>340</v>
+      </c>
       <c r="I33" s="7" t="s">
-        <v>207</v>
+        <v>321</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>210</v>
+        <v>323</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F34" s="7"/>
+      <c r="E34" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="G34" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>126</v>
+        <v>340</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="J34" s="7"/>
+        <v>321</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="35" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="4" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F35" s="7"/>
+        <v>123</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>326</v>
+      </c>
       <c r="G35" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>130</v>
+        <v>340</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="J35" s="7"/>
+        <v>327</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="36" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F36" s="7"/>
+        <v>123</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>328</v>
+      </c>
       <c r="G36" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>134</v>
+        <v>340</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="J36" s="7"/>
+        <v>329</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="37" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F37" s="7"/>
+        <v>123</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>332</v>
+      </c>
       <c r="G37" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>138</v>
+        <v>340</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="J37" s="7"/>
+        <v>330</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="38" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F38" s="7"/>
+        <v>123</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>333</v>
+      </c>
       <c r="G38" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>142</v>
+        <v>340</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="J38" s="7"/>
+        <v>330</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="39" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F39" s="7"/>
+        <v>123</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>335</v>
+      </c>
       <c r="G39" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>146</v>
+        <v>340</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="J39" s="7"/>
+        <v>330</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>334</v>
+      </c>
     </row>
     <row r="40" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>342</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>149</v>
+        <v>352</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F40" s="7"/>
+        <v>341</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>359</v>
+      </c>
       <c r="G40" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>150</v>
+        <v>380</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="J40" s="7"/>
+        <v>353</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>354</v>
+      </c>
     </row>
     <row r="41" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="4" t="s">
-        <v>152</v>
+        <v>343</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>153</v>
+        <v>355</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="F41" s="7"/>
+        <v>341</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>358</v>
+      </c>
       <c r="G41" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>154</v>
+        <v>380</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="J41" s="7"/>
+        <v>356</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>357</v>
+      </c>
     </row>
     <row r="42" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>344</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>157</v>
+        <v>360</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="F42" s="7"/>
-      <c r="G42" s="4" t="s">
-        <v>65</v>
+        <v>341</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>277</v>
+        <v>380</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="J42" s="7"/>
+        <v>363</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>361</v>
+      </c>
     </row>
     <row r="43" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F46" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="G46" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="I46" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="C43" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D43" s="6" t="s">
+      <c r="J46" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E48" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E43" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F43" s="7"/>
-      <c r="G43" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="J43" s="7"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A44" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D44" s="6" t="s">
+      <c r="F48" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="I53" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F54" s="7"/>
+      <c r="G54" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="I54" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="J54" s="7"/>
+    </row>
+    <row r="55" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F55" s="7"/>
+      <c r="G55" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="J55" s="7"/>
+    </row>
+    <row r="56" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F56" s="7"/>
+      <c r="G56" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="J56" s="7"/>
+    </row>
+    <row r="57" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E57" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E44" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="F44" s="7"/>
-      <c r="G44" s="4">
-        <v>0</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="I44" s="7"/>
-      <c r="J44" s="7"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A45" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="F45" s="7"/>
-      <c r="G45" s="4">
-        <v>0</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="I45" s="7"/>
-      <c r="J45" s="7"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A46" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="F46" s="7"/>
-      <c r="G46" s="4">
-        <v>0</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="I46" s="7"/>
-      <c r="J46" s="7"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A47" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E47" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="F47" s="7"/>
-      <c r="G47" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="J57" s="7"/>
+    </row>
+    <row r="58" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F58" s="7"/>
+      <c r="G58" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="I58" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="J58" s="7"/>
+    </row>
+    <row r="59" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F59" s="7"/>
+      <c r="G59" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="J59" s="7"/>
+    </row>
+    <row r="60" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F60" s="7"/>
+      <c r="G60" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I60" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="J60" s="7"/>
+    </row>
+    <row r="61" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F61" s="7"/>
+      <c r="G61" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="J61" s="7"/>
+    </row>
+    <row r="62" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F62" s="7"/>
+      <c r="G62" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="J62" s="7"/>
+    </row>
+    <row r="63" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A63" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F63" s="7"/>
+      <c r="G63" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I63" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="J63" s="7"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A64" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F64" s="7"/>
+      <c r="G64" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="I64" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="J64" s="7"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A65" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="F65" s="7"/>
+      <c r="G65" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="I65" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="J65" s="7"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A66" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="F66" s="7"/>
+      <c r="G66" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="I66" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="J66" s="7"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A67" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="F67" s="7"/>
+      <c r="G67" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="J67" s="7"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A68" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" s="10" t="s">
+        <v>338</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J43" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:J63" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/tools/menu-workbook/menu-data.xlsx
+++ b/tools/menu-workbook/menu-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\BackUp\AI+网络项目孵化\Baby_Menu_Applet\tools\menu-workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{994D827C-73CB-4134-A015-8CD5B9AAAEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A61F906D-F89B-4497-801E-F1F43005A13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6900" yWindow="2280" windowWidth="28800" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Categories!$A$1:$C$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Dishes!$A$1:$J$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Dishes!$A$1:$J$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Shop!$A$1:$G$2</definedName>
   </definedNames>
   <calcPr calcId="181029" forceFullCalc="1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="405">
   <si>
     <t>dishId</t>
   </si>
@@ -168,18 +168,12 @@
     <t>dessert01</t>
   </si>
   <si>
-    <t>榴莲千层</t>
-  </si>
-  <si>
     <t>dessert</t>
   </si>
   <si>
     <t>甜品</t>
   </si>
   <si>
-    <t>dessert01.jpg</t>
-  </si>
-  <si>
     <t>dessert02</t>
   </si>
   <si>
@@ -190,9 +184,6 @@
   </si>
   <si>
     <t>Tanghulu.jpg</t>
-  </si>
-  <si>
-    <t>dessert03</t>
   </si>
   <si>
     <t>蛋挞</t>
@@ -925,9 +916,6 @@
     <t>92</t>
   </si>
   <si>
-    <t>ChaPanda</t>
-  </si>
-  <si>
     <t>茶百道</t>
   </si>
   <si>
@@ -1325,6 +1313,99 @@
     <t>辣度: 不辣、微辣
 香菜：多香菜、少香菜、不要香菜</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>古茗</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dumpling3.jpg</t>
+  </si>
+  <si>
+    <t>sleep1.jpg</t>
+  </si>
+  <si>
+    <t>ChaPanda</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dessert04</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰淇淋</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ice-cream.jpg</t>
+  </si>
+  <si>
+    <t>宝宝想吃哪家的，可以写在备注里</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dessert03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dessert05</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>詹记</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>30</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>zhanji.jpg</t>
+  </si>
+  <si>
+    <t>蛋糕</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>cake.jpg</t>
+  </si>
+  <si>
+    <t>main08</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔斯汀</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>38</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ta_si_ting.jpg</t>
+  </si>
+  <si>
+    <t>main09</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>35</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>汉堡王</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>hamburger.jpg</t>
   </si>
 </sst>
 </file>
@@ -1769,42 +1850,42 @@
   <sheetData>
     <row r="1" spans="1:1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -1827,48 +1908,48 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>272</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -1900,10 +1981,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>14</v>
@@ -1922,10 +2003,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>24</v>
@@ -1933,10 +2014,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>48</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>29</v>
@@ -1944,134 +2025,134 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
-        <v>284</v>
+        <v>383</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -2087,7 +2168,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -2325,125 +2406,129 @@
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
-        <v>45</v>
+        <v>397</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>46</v>
+        <v>398</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>399</v>
       </c>
       <c r="F9" s="9"/>
       <c r="G9" s="4" t="s">
-        <v>15</v>
+        <v>393</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I9" s="7"/>
+        <v>400</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
-        <v>50</v>
+        <v>401</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>51</v>
+        <v>403</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>52</v>
+        <v>402</v>
       </c>
       <c r="F10" s="9"/>
       <c r="G10" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I10" s="7"/>
+        <v>404</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="J10" s="7"/>
     </row>
     <row r="11" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>55</v>
+        <v>395</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>20</v>
+      <c r="E11" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="F11" s="9"/>
       <c r="G11" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>56</v>
+        <v>396</v>
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
     <row r="12" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
-        <v>374</v>
+        <v>48</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>59</v>
+        <v>46</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="F12" s="9"/>
       <c r="G12" s="4" t="s">
-        <v>372</v>
+        <v>15</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
     </row>
     <row r="13" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
-        <v>61</v>
+        <v>389</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>59</v>
+        <v>46</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>20</v>
@@ -2453,596 +2538,576 @@
         <v>15</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
     </row>
     <row r="14" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>63</v>
+        <v>385</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>59</v>
+        <v>46</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="9"/>
+        <v>388</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>387</v>
+      </c>
       <c r="G14" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I14" s="7"/>
+        <v>386</v>
+      </c>
       <c r="J14" s="7"/>
     </row>
     <row r="15" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>371</v>
+        <v>391</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>59</v>
+        <v>46</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="9"/>
+        <v>392</v>
+      </c>
+      <c r="F15" s="7"/>
       <c r="G15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7" t="s">
-        <v>373</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="J15" s="7"/>
     </row>
     <row r="16" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>378</v>
+        <v>54</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="4"/>
+        <v>368</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="I16" s="7"/>
-      <c r="J16" s="7" t="s">
-        <v>379</v>
-      </c>
+      <c r="J16" s="7"/>
     </row>
     <row r="17" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>68</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="9"/>
       <c r="G17" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>71</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
     </row>
     <row r="18" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
-        <v>72</v>
+        <v>372</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>74</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="9"/>
       <c r="G18" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>76</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
     </row>
     <row r="19" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="4" t="s">
-        <v>77</v>
+        <v>371</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>78</v>
+        <v>367</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>79</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="9"/>
       <c r="G19" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>80</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="I19" s="7"/>
       <c r="J19" s="7" t="s">
-        <v>81</v>
+        <v>369</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="4" t="s">
-        <v>82</v>
+        <v>373</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>83</v>
+        <v>374</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>84</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="9"/>
       <c r="G20" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>85</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="I20" s="7"/>
       <c r="J20" s="7" t="s">
-        <v>86</v>
+        <v>375</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="4" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="I21" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>90</v>
-      </c>
       <c r="J21" s="7" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="I22" s="7" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="I23" s="7" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="4" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="C24" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="I24" s="7" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="4" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="C25" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="I25" s="7" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="4" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="I26" s="7" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="4" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>14</v>
+        <v>63</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>305</v>
+        <v>97</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>340</v>
+        <v>66</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>306</v>
+        <v>98</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>308</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="4" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>20</v>
+        <v>63</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>102</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>309</v>
+        <v>103</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>340</v>
+        <v>66</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>313</v>
+        <v>104</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>311</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="4" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>24</v>
+        <v>63</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>108</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>310</v>
+        <v>109</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>340</v>
+        <v>66</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>314</v>
+        <v>110</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>311</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>29</v>
+        <v>63</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>312</v>
+        <v>115</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>340</v>
+        <v>66</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>314</v>
+        <v>116</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>311</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="4" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>317</v>
+        <v>304</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>318</v>
+        <v>122</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="J32" s="7" t="s">
         <v>307</v>
@@ -3050,1093 +3115,1221 @@
     </row>
     <row r="33" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="4" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="4" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>141</v>
+        <v>129</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>314</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>117</v>
+        <v>39</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>147</v>
+        <v>102</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="4" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="4" t="s">
-        <v>342</v>
+        <v>137</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>352</v>
+        <v>138</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>279</v>
+        <v>120</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>347</v>
+        <v>114</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>359</v>
+        <v>324</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>380</v>
+        <v>336</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>353</v>
+        <v>325</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>354</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="4" t="s">
-        <v>343</v>
+        <v>139</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>355</v>
+        <v>140</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>279</v>
+        <v>120</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>348</v>
+        <v>141</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>358</v>
+        <v>328</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>380</v>
+        <v>336</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>357</v>
+        <v>327</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="4" t="s">
-        <v>344</v>
+        <v>142</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>360</v>
+        <v>143</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>279</v>
+        <v>120</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>349</v>
+        <v>144</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="G42" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="G42" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>380</v>
+        <v>336</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>363</v>
+        <v>326</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>361</v>
+        <v>327</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="4" t="s">
-        <v>345</v>
+        <v>145</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>364</v>
+        <v>130</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>279</v>
+        <v>120</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>350</v>
+        <v>146</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>366</v>
+        <v>331</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>381</v>
+        <v>336</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>365</v>
+        <v>326</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>367</v>
+        <v>330</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="4" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>279</v>
+        <v>380</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>151</v>
+        <v>339</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>351</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>152</v>
+        <v>337</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>14</v>
+        <v>276</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>344</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>154</v>
+        <v>354</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>155</v>
+        <v>352</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>156</v>
+        <v>353</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>158</v>
+        <v>340</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>356</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>152</v>
+        <v>337</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>20</v>
+        <v>276</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>345</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G46" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="G46" s="12" t="s">
         <v>15</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>160</v>
+        <v>359</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>161</v>
+        <v>357</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>163</v>
+        <v>341</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>360</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>152</v>
+        <v>337</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>24</v>
+        <v>276</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>346</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>164</v>
+        <v>362</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>165</v>
+        <v>361</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>166</v>
+        <v>363</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>168</v>
+        <v>342</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>364</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>152</v>
+        <v>337</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>29</v>
+        <v>276</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>347</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>169</v>
+        <v>366</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>170</v>
+        <v>365</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>171</v>
+        <v>363</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="4" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="C49" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="I49" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="J49" s="7" t="s">
         <v>153</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="I49" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="4" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="4" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="4" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="G52" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="4" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>196</v>
+        <v>174</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>175</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F54" s="7"/>
+        <v>149</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>176</v>
+      </c>
       <c r="G54" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>199</v>
+        <v>378</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="J54" s="7"/>
+        <v>177</v>
+      </c>
+      <c r="J54" s="7" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="55" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>202</v>
+        <v>179</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F55" s="7"/>
+        <v>149</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>181</v>
+      </c>
       <c r="G55" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>203</v>
+        <v>378</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="J55" s="7"/>
+        <v>182</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="56" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>206</v>
+        <v>183</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>184</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F56" s="7"/>
+        <v>149</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>185</v>
+      </c>
       <c r="G56" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>207</v>
+        <v>378</v>
       </c>
       <c r="I56" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="J56" s="7"/>
+        <v>186</v>
+      </c>
+      <c r="J56" s="7" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="57" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>210</v>
+        <v>187</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F57" s="7"/>
+        <v>149</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>189</v>
+      </c>
       <c r="G57" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>211</v>
+        <v>378</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="J57" s="7"/>
+        <v>190</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="58" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F58" s="7"/>
       <c r="G58" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="J58" s="7"/>
     </row>
     <row r="59" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="4" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F59" s="7"/>
       <c r="G59" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="J59" s="7"/>
     </row>
     <row r="60" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="4" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="I60" s="7" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="J60" s="7"/>
     </row>
     <row r="61" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="4" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="J61" s="7"/>
     </row>
     <row r="62" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="4" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="F62" s="7"/>
       <c r="G62" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="I62" s="7" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="J62" s="7"/>
     </row>
     <row r="63" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="4" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>117</v>
+        <v>39</v>
       </c>
       <c r="F63" s="7"/>
       <c r="G63" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="I63" s="7" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="J63" s="7"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="B64" s="10" t="s">
-        <v>237</v>
+        <v>217</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>218</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E64" s="11" t="s">
-        <v>43</v>
+        <v>195</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="F64" s="7"/>
       <c r="G64" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="I64" s="7" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="J64" s="7"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="B65" s="10" t="s">
-        <v>241</v>
+        <v>221</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>222</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E65" s="11" t="s">
-        <v>144</v>
+        <v>195</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>102</v>
       </c>
       <c r="F65" s="7"/>
       <c r="G65" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="J65" s="7"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="B66" s="10" t="s">
-        <v>245</v>
+        <v>225</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>226</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>246</v>
+        <v>195</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>108</v>
       </c>
       <c r="F66" s="7"/>
       <c r="G66" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="I66" s="7" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="J66" s="7"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="B67" s="10" t="s">
-        <v>250</v>
+        <v>229</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>230</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E67" s="11" t="s">
-        <v>251</v>
+        <v>195</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="F67" s="7"/>
       <c r="G67" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="J67" s="7"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A68" s="10" t="s">
-        <v>336</v>
+      <c r="A68" s="4" t="s">
+        <v>233</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>337</v>
+        <v>234</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E68" s="13" t="s">
-        <v>339</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F68" s="7"/>
       <c r="G68" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H68" s="10" t="s">
-        <v>338</v>
+      <c r="H68" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="I68" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="J68" s="7"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A69" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="F69" s="7"/>
+      <c r="G69" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="I69" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="J69" s="7"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A70" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="F70" s="7"/>
+      <c r="G70" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I70" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="J70" s="7"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A71" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="F71" s="7"/>
+      <c r="G71" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="J71" s="7"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A72" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H72" s="10" t="s">
+        <v>334</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J63" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:J67" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
